--- a/artfynd/A 46671-2024 artfynd.xlsx
+++ b/artfynd/A 46671-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121144013</v>
+        <v>121143712</v>
       </c>
       <c r="B2" t="n">
-        <v>79216</v>
+        <v>90662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571998</v>
+        <v>571993</v>
       </c>
       <c r="R2" t="n">
-        <v>6511657</v>
+        <v>6511689</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143945</v>
+        <v>121143593</v>
       </c>
       <c r="B3" t="n">
-        <v>74644</v>
+        <v>79219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ämten, Ämten, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572127</v>
+        <v>571991</v>
       </c>
       <c r="R3" t="n">
-        <v>6511614</v>
+        <v>6511689</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143540</v>
+        <v>121143945</v>
       </c>
       <c r="B4" t="n">
-        <v>79216</v>
+        <v>74647</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Ämten, Ämten, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571997</v>
+        <v>572127</v>
       </c>
       <c r="R4" t="n">
-        <v>6511680</v>
+        <v>6511614</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143593</v>
+        <v>121143540</v>
       </c>
       <c r="B5" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571991</v>
+        <v>571997</v>
       </c>
       <c r="R5" t="n">
-        <v>6511689</v>
+        <v>6511680</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121143577</v>
+        <v>121143909</v>
       </c>
       <c r="B6" t="n">
-        <v>94737</v>
+        <v>74647</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Ämten, Ämten, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571991</v>
+        <v>572160</v>
       </c>
       <c r="R6" t="n">
-        <v>6511689</v>
+        <v>6511578</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121143626</v>
+        <v>121143577</v>
       </c>
       <c r="B7" t="n">
-        <v>79216</v>
+        <v>94747</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572001</v>
+        <v>571991</v>
       </c>
       <c r="R7" t="n">
-        <v>6511682</v>
+        <v>6511689</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121143909</v>
+        <v>121143626</v>
       </c>
       <c r="B8" t="n">
-        <v>74644</v>
+        <v>79219</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,41 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ämten, Ämten, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572160</v>
+        <v>572001</v>
       </c>
       <c r="R8" t="n">
-        <v>6511578</v>
+        <v>6511682</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121143712</v>
+        <v>121144013</v>
       </c>
       <c r="B9" t="n">
-        <v>90652</v>
+        <v>79219</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571993</v>
+        <v>571998</v>
       </c>
       <c r="R9" t="n">
-        <v>6511689</v>
+        <v>6511657</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>

--- a/artfynd/A 46671-2024 artfynd.xlsx
+++ b/artfynd/A 46671-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143712</v>
+        <v>121143585</v>
       </c>
       <c r="B2" t="n">
-        <v>90662</v>
+        <v>79219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571993</v>
+        <v>571991</v>
       </c>
       <c r="R2" t="n">
         <v>6511689</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143593</v>
+        <v>121143626</v>
       </c>
       <c r="B3" t="n">
         <v>79219</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571991</v>
+        <v>572001</v>
       </c>
       <c r="R3" t="n">
-        <v>6511689</v>
+        <v>6511682</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121143909</v>
+        <v>121144013</v>
       </c>
       <c r="B6" t="n">
-        <v>74647</v>
+        <v>79219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ämten, Ämten, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572160</v>
+        <v>571998</v>
       </c>
       <c r="R6" t="n">
-        <v>6511578</v>
+        <v>6511657</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121143626</v>
+        <v>121143909</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>74647</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,41 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Ämten, Ämten, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572001</v>
+        <v>572160</v>
       </c>
       <c r="R8" t="n">
-        <v>6511682</v>
+        <v>6511578</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121144013</v>
+        <v>121143712</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>90662</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571998</v>
+        <v>571993</v>
       </c>
       <c r="R9" t="n">
-        <v>6511657</v>
+        <v>6511689</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>

--- a/artfynd/A 46671-2024 artfynd.xlsx
+++ b/artfynd/A 46671-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143585</v>
+        <v>121143540</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571991</v>
+        <v>571997</v>
       </c>
       <c r="R2" t="n">
-        <v>6511689</v>
+        <v>6511680</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143626</v>
+        <v>121143577</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>94759</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572001</v>
+        <v>571991</v>
       </c>
       <c r="R3" t="n">
-        <v>6511682</v>
+        <v>6511689</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143945</v>
+        <v>121143909</v>
       </c>
       <c r="B4" t="n">
-        <v>74647</v>
+        <v>74649</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572127</v>
+        <v>572160</v>
       </c>
       <c r="R4" t="n">
-        <v>6511614</v>
+        <v>6511578</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143540</v>
+        <v>121143593</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571997</v>
+        <v>571991</v>
       </c>
       <c r="R5" t="n">
-        <v>6511680</v>
+        <v>6511689</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121144013</v>
+        <v>121143626</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571998</v>
+        <v>572001</v>
       </c>
       <c r="R6" t="n">
-        <v>6511657</v>
+        <v>6511682</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121143577</v>
+        <v>121143945</v>
       </c>
       <c r="B7" t="n">
-        <v>94747</v>
+        <v>74649</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Ämten, Ämten, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571991</v>
+        <v>572127</v>
       </c>
       <c r="R7" t="n">
-        <v>6511689</v>
+        <v>6511614</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121143909</v>
+        <v>121144013</v>
       </c>
       <c r="B8" t="n">
-        <v>74647</v>
+        <v>79222</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,41 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ämten, Ämten, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572160</v>
+        <v>571998</v>
       </c>
       <c r="R8" t="n">
-        <v>6511578</v>
+        <v>6511657</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>121143712</v>
       </c>
       <c r="B9" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 46671-2024 artfynd.xlsx
+++ b/artfynd/A 46671-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143540</v>
+        <v>121143626</v>
       </c>
       <c r="B2" t="n">
         <v>79222</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571997</v>
+        <v>572001</v>
       </c>
       <c r="R2" t="n">
-        <v>6511680</v>
+        <v>6511682</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -780,7 +780,7 @@
         <v>121143577</v>
       </c>
       <c r="B3" t="n">
-        <v>94759</v>
+        <v>94760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143593</v>
+        <v>121143712</v>
       </c>
       <c r="B5" t="n">
-        <v>79222</v>
+        <v>90675</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571991</v>
+        <v>571993</v>
       </c>
       <c r="R5" t="n">
         <v>6511689</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121143626</v>
+        <v>121143585</v>
       </c>
       <c r="B6" t="n">
         <v>79222</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572001</v>
+        <v>571991</v>
       </c>
       <c r="R6" t="n">
-        <v>6511682</v>
+        <v>6511689</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121143945</v>
+        <v>121144013</v>
       </c>
       <c r="B7" t="n">
-        <v>74649</v>
+        <v>79222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,41 +1197,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ämten, Ämten, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572127</v>
+        <v>571998</v>
       </c>
       <c r="R7" t="n">
-        <v>6511614</v>
+        <v>6511657</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121144013</v>
+        <v>121143540</v>
       </c>
       <c r="B8" t="n">
         <v>79222</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571998</v>
+        <v>571997</v>
       </c>
       <c r="R8" t="n">
-        <v>6511657</v>
+        <v>6511680</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121143712</v>
+        <v>121143945</v>
       </c>
       <c r="B9" t="n">
-        <v>90674</v>
+        <v>74649</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,37 +1405,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Ämten, Ämten, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571993</v>
+        <v>572127</v>
       </c>
       <c r="R9" t="n">
-        <v>6511689</v>
+        <v>6511614</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 46671-2024 artfynd.xlsx
+++ b/artfynd/A 46671-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143626</v>
+        <v>121143909</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>74652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Ämten, Ämten, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572001</v>
+        <v>572160</v>
       </c>
       <c r="R2" t="n">
-        <v>6511682</v>
+        <v>6511578</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143577</v>
+        <v>121143540</v>
       </c>
       <c r="B3" t="n">
-        <v>94760</v>
+        <v>79225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571991</v>
+        <v>571997</v>
       </c>
       <c r="R3" t="n">
-        <v>6511689</v>
+        <v>6511680</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143909</v>
+        <v>121143945</v>
       </c>
       <c r="B4" t="n">
-        <v>74649</v>
+        <v>74652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572160</v>
+        <v>572127</v>
       </c>
       <c r="R4" t="n">
-        <v>6511578</v>
+        <v>6511614</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143712</v>
+        <v>121143626</v>
       </c>
       <c r="B5" t="n">
-        <v>90675</v>
+        <v>79225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571993</v>
+        <v>572001</v>
       </c>
       <c r="R5" t="n">
-        <v>6511689</v>
+        <v>6511682</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121143585</v>
+        <v>121144013</v>
       </c>
       <c r="B6" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571991</v>
+        <v>571998</v>
       </c>
       <c r="R6" t="n">
-        <v>6511689</v>
+        <v>6511657</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121144013</v>
+        <v>121143712</v>
       </c>
       <c r="B7" t="n">
-        <v>79222</v>
+        <v>90678</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571998</v>
+        <v>571993</v>
       </c>
       <c r="R7" t="n">
-        <v>6511657</v>
+        <v>6511689</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121143540</v>
+        <v>121143577</v>
       </c>
       <c r="B8" t="n">
-        <v>79222</v>
+        <v>94763</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571997</v>
+        <v>571991</v>
       </c>
       <c r="R8" t="n">
-        <v>6511680</v>
+        <v>6511689</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121143945</v>
+        <v>121143585</v>
       </c>
       <c r="B9" t="n">
-        <v>74649</v>
+        <v>79225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,41 +1401,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ämten, Ämten, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572127</v>
+        <v>571991</v>
       </c>
       <c r="R9" t="n">
-        <v>6511614</v>
+        <v>6511689</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 46671-2024 artfynd.xlsx
+++ b/artfynd/A 46671-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143909</v>
+        <v>121143577</v>
       </c>
       <c r="B2" t="n">
-        <v>74652</v>
+        <v>94763</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ämten, Ämten, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572160</v>
+        <v>571991</v>
       </c>
       <c r="R2" t="n">
-        <v>6511578</v>
+        <v>6511689</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143540</v>
+        <v>121143626</v>
       </c>
       <c r="B3" t="n">
         <v>79225</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571997</v>
+        <v>572001</v>
       </c>
       <c r="R3" t="n">
-        <v>6511680</v>
+        <v>6511682</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143945</v>
+        <v>121143593</v>
       </c>
       <c r="B4" t="n">
-        <v>74652</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ämten, Ämten, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572127</v>
+        <v>571991</v>
       </c>
       <c r="R4" t="n">
-        <v>6511614</v>
+        <v>6511689</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143626</v>
+        <v>121143945</v>
       </c>
       <c r="B5" t="n">
-        <v>79225</v>
+        <v>74652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Ämten, Ämten, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572001</v>
+        <v>572127</v>
       </c>
       <c r="R5" t="n">
-        <v>6511682</v>
+        <v>6511614</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121143712</v>
+        <v>121143540</v>
       </c>
       <c r="B7" t="n">
-        <v>90678</v>
+        <v>79225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571993</v>
+        <v>571997</v>
       </c>
       <c r="R7" t="n">
-        <v>6511689</v>
+        <v>6511680</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121143577</v>
+        <v>121143712</v>
       </c>
       <c r="B8" t="n">
-        <v>94763</v>
+        <v>90678</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571991</v>
+        <v>571993</v>
       </c>
       <c r="R8" t="n">
         <v>6511689</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121143585</v>
+        <v>121143909</v>
       </c>
       <c r="B9" t="n">
-        <v>79225</v>
+        <v>74652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,41 +1401,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Ämten, Ämten, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571991</v>
+        <v>572160</v>
       </c>
       <c r="R9" t="n">
-        <v>6511689</v>
+        <v>6511578</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 46671-2024 artfynd.xlsx
+++ b/artfynd/A 46671-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143577</v>
+        <v>121143945</v>
       </c>
       <c r="B2" t="n">
-        <v>94763</v>
+        <v>74652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Ämten, Ämten, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571991</v>
+        <v>572127</v>
       </c>
       <c r="R2" t="n">
-        <v>6511689</v>
+        <v>6511614</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143626</v>
+        <v>121143909</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
+        <v>74652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Ämten, Ämten, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572001</v>
+        <v>572160</v>
       </c>
       <c r="R3" t="n">
-        <v>6511682</v>
+        <v>6511578</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,618 +876,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>121143593</v>
-      </c>
-      <c r="B4" t="n">
-        <v>79225</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Åfallet, Åfallet, Ög</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>571991</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6511689</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Simonstorp</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>121143945</v>
-      </c>
-      <c r="B5" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Felipes leucopellaeus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ämten, Ämten, Ög</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>572127</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6511614</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Simonstorp</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>121144013</v>
-      </c>
-      <c r="B6" t="n">
-        <v>79225</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Åfallet, Åfallet, Ög</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>571998</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6511657</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Simonstorp</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>121143540</v>
-      </c>
-      <c r="B7" t="n">
-        <v>79225</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Åfallet, Åfallet, Ög</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>571997</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6511680</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Simonstorp</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>121143712</v>
-      </c>
-      <c r="B8" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Åfallet, Åfallet, Ög</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>571993</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6511689</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Simonstorp</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>121143909</v>
-      </c>
-      <c r="B9" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Felipes leucopellaeus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Ämten, Ämten, Ög</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>572160</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6511578</v>
-      </c>
-      <c r="S9" t="n">
-        <v>7</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Simonstorp</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46671-2024 artfynd.xlsx
+++ b/artfynd/A 46671-2024 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143945</v>
+        <v>121143909</v>
       </c>
       <c r="B2" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572127</v>
+        <v>572160</v>
       </c>
       <c r="R2" t="n">
-        <v>6511614</v>
+        <v>6511578</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143909</v>
+        <v>121143945</v>
       </c>
       <c r="B3" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572160</v>
+        <v>572127</v>
       </c>
       <c r="R3" t="n">
-        <v>6511578</v>
+        <v>6511614</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 46671-2024 artfynd.xlsx
+++ b/artfynd/A 46671-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143909</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143945</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>